--- a/cerebro-londres/Diccionario_de_datos_TallerDatos.xlsx
+++ b/cerebro-londres/Diccionario_de_datos_TallerDatos.xlsx
@@ -574,21 +574,21 @@
     <row r="5">
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>Ciudad elegida:</t>
+          <t>Ciudad elegida: Londres</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>Integrantes:</t>
+          <t>Integrantes: Jean Carlo Ardila - David Cossio - Juan Pablo Posso</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>Enlace al repositorio o a la carpeta del lago:</t>
+          <t>Enlace al repositorio o a la carpeta del lago: https://github.com/JeanArdila711/cerebro-londres</t>
         </is>
       </c>
     </row>

--- a/cerebro-londres/Diccionario_de_datos_TallerDatos.xlsx
+++ b/cerebro-londres/Diccionario_de_datos_TallerDatos.xlsx
@@ -693,7 +693,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P44"/>
+  <dimension ref="A1:P50"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -1144,7 +1144,7 @@
       </c>
       <c r="B8" s="10" t="inlineStr">
         <is>
-          <t>Delitos callejeros registrados en Westminster, últimos 12 meses (data.police.uk)</t>
+          <t>Delitos callejeros registrados en Westminster, hasta 12 meses pedidos (data.police.uk)</t>
         </is>
       </c>
       <c r="C8" s="10" t="inlineStr">
@@ -1189,7 +1189,7 @@
       </c>
       <c r="K8" s="10" t="inlineStr">
         <is>
-          <t>últimos 12 meses móviles</t>
+          <t>hasta 12 meses móviles (puede haber menos: algún mes puede caer sin dato por la API)</t>
         </is>
       </c>
       <c r="L8" s="10" t="inlineStr">
@@ -1199,7 +1199,7 @@
       </c>
       <c r="M8" s="10" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="N8" s="10" t="inlineStr">
@@ -1214,7 +1214,7 @@
       </c>
       <c r="P8" s="10" t="inlineStr">
         <is>
-          <t>La API trae un registro por delito con coordenadas (desplazadas a un punto ancla, no la dirección exacta). Decisión de privacidad ya tomada: al lago solo entran conteos agregados por categoría y mes, nunca el registro individual, y el crudo no se versiona.</t>
+          <t>La API trae un registro por delito con coordenadas (desplazadas a un punto ancla, no la dirección exacta). Decisión de privacidad ya tomada: al lago solo entran conteos agregados por categoría y mes, nunca el registro individual, y el crudo no se versiona. Se piden 12 meses pero no siempre responden los 12: la prueba de hoy trajo 11 (1 mes sin dato), número que varía de una corrida a otra; el lago lo declara en meses_sin_dato, no lo esconde.</t>
         </is>
       </c>
     </row>
@@ -1460,7 +1460,7 @@
       </c>
       <c r="P11" s="10" t="inlineStr">
         <is>
-          <t>Contiene OS data © Crown copyright and database right. Tres capas de la misma fuente, en ingesta/pull_territorio.py: territorio/boroughs.geojson (33), territorio/wards_westminster.geojson (18, cosecha 2024) y territorio/wards_londres.geojson (704, cosecha 2025). Hallazgo corregido: se creía que la capa de wards de 2025 solo existía como MapServer; con el nombre de servicio correcto (WD_DEC_2025_UK_BGC) sí es FeatureServer y responde.</t>
+          <t>Contiene OS data © Crown copyright and database right. Tres capas de la misma fuente, en ingesta/pull_territorio.py: territorio/boroughs.geojson (33), territorio/wards_westminster.geojson (18, cosecha 2024) y territorio/wards_londres.geojson (704, cosecha 2025). Hallazgo corregido: se creía que la capa de wards de 2025 solo existía como MapServer; con el nombre de servicio correcto (WD_DEC_2025_UK_BGC) sí es FeatureServer y responde. OJO (revisión del profesor): el área de cada borough (atlas_boroughs.json, para densidad) se calculaba con una fórmula esférica sobre grados lon/lat. Se corrigió proyectando a metros con la Transverse Mercator del British National Grid (EPSG:27700) antes del shoelace: Westminster pasó de 21,38 a 21,45 km², diferencia chica pero el método anterior no era correcto para un plano métrico.</t>
         </is>
       </c>
     </row>
@@ -2116,7 +2116,7 @@
       </c>
       <c r="P19" s="10" t="inlineStr">
         <is>
-          <t>La licencia permite reutilizarla, pero cada registro trae edad, sexo, etnia autopercibida, motivo y ubicación aproximada de una persona detenida: entraría identificable aunque la licencia lo permita. Se descarta el registro individual; el MPS ya publica un tablero agregado por borough y mes que sí sirve (fuente candidata aparte, ver la familia de seguridad del catálogo). Dato que podría hacer daño si se cruza con otro (pregunta 5 del documento de justificación).</t>
+          <t>La licencia permite reutilizarla, pero cada registro trae edad, sexo, etnia autopercibida, motivo y ubicación aproximada de una persona detenida: entraría identificable aunque la licencia lo permita. Se descarta el registro individual; el MPS ya publica un tablero agregado por borough y mes que sí sirve (fuente candidata aparte, ver la familia de seguridad del catálogo). Dato que podría hacer daño si se cruza con otro (mismo principio de daño por cruce que el campo lsoa_mas_privado de F12, pregunta 5 del documento de justificación).</t>
         </is>
       </c>
     </row>
@@ -2280,7 +2280,7 @@
       </c>
       <c r="P21" s="10" t="inlineStr">
         <is>
-          <t>El conjunto trae tres resoluciones (ward, borough, LSOA) con decenas de copias históricas con el mismo nombre; la fecha del portal no sirve para elegir la más reciente (viene vacía), así que se comparó la cabecera de varias copias hasta encontrar la que llega a agosto de 2026. Cruzado por nombre contra los boroughs del ONS: 32 coinciden letra por letra. 'Aviation Policing' (Heathrow) y 'Unknown' se cuentan aparte, nunca se reparten. Ya integrada: ingesta/pull_seguridad_boroughs.py, lago/seguridad_boroughs.json. Hallazgo: Westminster tiene la tasa más alta de los 32 (350,6 por 1.000 hab., frente a 58,1 de Richmond upon Thames).</t>
+          <t>El conjunto trae tres resoluciones (ward, borough, LSOA) con decenas de copias históricas con el mismo nombre; la fecha del portal no sirve para elegir la más reciente (viene vacía), así que se comparó la cabecera de varias copias hasta encontrar la que llega a agosto de 2026. Cruzado por nombre contra los boroughs del ONS: 32 coinciden letra por letra. 'Aviation Policing' (Heathrow) y 'Unknown' se cuentan aparte, nunca se reparten. Ya integrada: ingesta/pull_seguridad_boroughs.py, lago/seguridad_boroughs.json. Hallazgo: Westminster tiene la tasa más alta de los 32 (350,6 por 1.000 hab., frente a 58,1 de Richmond upon Thames). OJO (revisión del profesor): la tasa por 1.000 habitantes divide sobre población RESIDENTE mid-year, no sobre quien está físicamente en el borough. Westminster recibe a diario miles de trabajadores, turistas y gente de paso que este denominador no cuenta: la tasa por residente sobreestima su inseguridad frente a la población flotante real.</t>
         </is>
       </c>
     </row>
@@ -2352,7 +2352,7 @@
       </c>
       <c r="N22" s="10" t="inlineStr">
         <is>
-          <t>Candidata</t>
+          <t>Descartada</t>
         </is>
       </c>
       <c r="O22" s="10" t="inlineStr">
@@ -2362,7 +2362,7 @@
       </c>
       <c r="P22" s="10" t="inlineStr">
         <is>
-          <t>El equivalente al SEACE de Lima. Formato OCDS estándar. Sirve para la pregunta «cómo se financia el municipio» del taller, del lado del gasto, no solo del presupuesto.</t>
+          <t>Descartada: la licencia (OGL-3.0) sí permite reutilizarla, pero un registro real trae nombre, correo y celular de una persona (una funcionaria de un NHS Trust) en el campo contactPoint, y la API no tiene filtro geográfico confiable para limitarse a Londres. El equivalente al SEACE de Lima, para la pregunta «cómo se financia el municipio» del lado del gasto, no solo del presupuesto — queda pendiente.</t>
         </is>
       </c>
     </row>
@@ -2414,7 +2414,7 @@
       </c>
       <c r="J23" s="10" t="inlineStr">
         <is>
-          <t>21-22 de los 33 boroughs (el resto no tiene estación activa un día dado)</t>
+          <t>Varía día a día: entre 14 y 22 de los 33 boroughs en las pruebas hechas (el resto no tiene estación activa ese día)</t>
         </is>
       </c>
       <c r="K23" s="10" t="inlineStr">
@@ -2429,7 +2429,7 @@
       </c>
       <c r="M23" s="10" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="N23" s="10" t="inlineStr">
@@ -2444,7 +2444,7 @@
       </c>
       <c r="P23" s="10" t="inlineStr">
         <is>
-          <t>URL cambió frente a la candidata original: esa era solo metadatos de estaciones; esta es el dato real del día. Ya integrada: ingesta/pull_aire_laqn.py, lago/aire_laqn.json. CORRECCIÓN sobre mi primer intento: convertí la banda de texto (Low/Moderate/High) a un número propio de 1 a 4 y todo dio empatado en 1 — el mismo error que el taller critica en el tsunami de Lima (todo en cero, pero igual se nombra «la zona más expuesta»). Se corrigió usando el índice numérico real de la fuente (escala DAQI 1-10), que sí varía (1,0 a 3,0 el día probado).</t>
+          <t>URL cambió frente a la candidata original: esa era solo metadatos de estaciones; esta es el dato real del día. Ya integrada: ingesta/pull_aire_laqn.py, lago/aire_laqn.json. CORRECCIÓN 1 (sobre el primer intento): convertí la banda de texto (Low/Moderate/High) a un número propio de 1 a 4 y todo dio empatado en 1 — el mismo error que el taller critica en el tsunami de Lima (todo en cero, pero igual se nombra «la zona más expuesta»). CORRECCIÓN 2 (revisión del profesor): el índice por estación promediaba todas las especies medidas entre sí, mezclando contaminantes no comparables. El DAQI real toma el MÁXIMO por contaminante en cada estación, no el promedio: se corrigió así. El número de boroughs con estación activa varía por día, no es una cifra fija.</t>
         </is>
       </c>
     </row>
@@ -4170,6 +4170,12 @@
         </is>
       </c>
     </row>
+    <row r="45"/>
+    <row r="46"/>
+    <row r="47"/>
+    <row r="48"/>
+    <row r="49"/>
+    <row r="50"/>
   </sheetData>
   <dataValidations count="6">
     <dataValidation sqref="D5:D44" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" error="Elijan una opción de la lista" type="list">
@@ -4859,7 +4865,7 @@
       </c>
       <c r="E12" s="10" t="inlineStr">
         <is>
-          <t>Delitos registrados en Westminster en los últimos 12 meses descargados</t>
+          <t>Delitos registrados en Westminster, suma de los meses descargados (hasta 12 pedidos; puede haber menos por caídas puntuales de la API)</t>
         </is>
       </c>
       <c r="F12" s="10" t="inlineStr">
@@ -4874,7 +4880,7 @@
       </c>
       <c r="H12" s="10" t="inlineStr">
         <is>
-          <t>90008</t>
+          <t>90008 (ejemplo de una corrida con 11 de 12 meses)</t>
         </is>
       </c>
       <c r="I12" s="10" t="inlineStr">
@@ -4894,7 +4900,7 @@
       </c>
       <c r="L12" s="10" t="inlineStr">
         <is>
-          <t>Suma de 10 meses descargados por categoría; cuenta delitos, no víctimas</t>
+          <t>Suma del conteo por categoría de los meses que sí respondieron (hasta 12, nunca más)</t>
         </is>
       </c>
       <c r="M12" s="10" t="inlineStr">
@@ -6466,7 +6472,7 @@
       </c>
       <c r="E36" s="10" t="inlineStr">
         <is>
-          <t>Índice de calidad del aire de Westminster, promedio de sus estaciones activas, un día</t>
+          <t>Índice de calidad del aire de Westminster: promedio, entre sus estaciones activas, del máximo por contaminante de cada una (DAQI real)</t>
         </is>
       </c>
       <c r="F36" s="10" t="inlineStr">
@@ -6501,7 +6507,7 @@
       </c>
       <c r="L36" s="10" t="inlineStr">
         <is>
-          <t>Promedio de las lecturas por especie de las estaciones LAQN activas en Westminster</t>
+          <t>Por estación: máximo entre sus contaminantes (DAQI real, no promedio entre especies). Por borough: promedio de esos máximos entre sus estaciones</t>
         </is>
       </c>
       <c r="M36" s="10" t="inlineStr">
@@ -6543,7 +6549,7 @@
       </c>
       <c r="G37" s="10" t="inlineStr">
         <is>
-          <t>puesto de 18</t>
+          <t>puesto de N (varía: entre 14 y 22 boroughs con estación activa, según el día)</t>
         </is>
       </c>
       <c r="H37" s="10" t="inlineStr">
@@ -6558,7 +6564,7 @@
       </c>
       <c r="J37" s="10" t="inlineStr">
         <is>
-          <t>1 a 18 (varía según el día)</t>
+          <t>1 a 33 (el denominador varía según el día)</t>
         </is>
       </c>
       <c r="K37" s="10" t="inlineStr">
@@ -6912,19 +6918,71 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="10" t="n"/>
-      <c r="B43" s="10" t="n"/>
-      <c r="C43" s="10" t="n"/>
-      <c r="D43" s="10" t="n"/>
-      <c r="E43" s="10" t="n"/>
-      <c r="F43" s="10" t="n"/>
-      <c r="G43" s="10" t="n"/>
-      <c r="H43" s="10" t="n"/>
-      <c r="I43" s="10" t="n"/>
-      <c r="J43" s="10" t="n"/>
-      <c r="K43" s="10" t="n"/>
-      <c r="L43" s="10" t="n"/>
-      <c r="M43" s="10" t="n"/>
+      <c r="A43" s="10" t="inlineStr">
+        <is>
+          <t>F12</t>
+        </is>
+      </c>
+      <c r="B43" s="10" t="inlineStr">
+        <is>
+          <t>lago/privacion.json</t>
+        </is>
+      </c>
+      <c r="C43" s="10" t="inlineStr">
+        <is>
+          <t>lsoa_mas_privado / lsoa_menos_privado</t>
+        </is>
+      </c>
+      <c r="D43" s="10" t="inlineStr">
+        <is>
+          <t>(se calcula: min/max sobre rank nacional IMD)</t>
+        </is>
+      </c>
+      <c r="E43" s="10" t="inlineStr">
+        <is>
+          <t>El LSOA (unidad censal, ~1.500 hab.) más y menos privado de Westminster, por rank nacional IMD 2025</t>
+        </is>
+      </c>
+      <c r="F43" s="10" t="inlineStr">
+        <is>
+          <t>Texto</t>
+        </is>
+      </c>
+      <c r="G43" s="10" t="inlineStr">
+        <is>
+          <t>nombre de LSOA</t>
+        </is>
+      </c>
+      <c r="H43" s="10" t="inlineStr">
+        <is>
+          <t>Westminster 020B</t>
+        </is>
+      </c>
+      <c r="I43" s="10" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J43" s="10" t="inlineStr">
+        <is>
+          <t>uno de los 123 LSOA de Westminster</t>
+        </is>
+      </c>
+      <c r="K43" s="10" t="inlineStr">
+        <is>
+          <t>Pública</t>
+        </is>
+      </c>
+      <c r="L43" s="10" t="inlineStr">
+        <is>
+          <t>min()/max() del rank nacional entre los 123 LSOA de Westminster (rank 1 = el más privado del país)</t>
+        </is>
+      </c>
+      <c r="M43" s="10" t="inlineStr">
+        <is>
+          <t>El campo más delicado del lago: nombra una unidad censal concreta como la más privada de Inglaterra (pregunta 5 del documento de justificación)</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="10" t="n"/>
